--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KillianMathieu\Documents\Egis\ERP_Commander_Robot5\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KillianMathieu\Documents\UiPath\Egis\Egis-Robot1\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25E0CCC-4F5E-4F15-A22D-F266FD334326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0094784B-0641-4FAB-867C-AD1CCC65FA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -201,7 +201,7 @@
     <t>LicenceNumber</t>
   </si>
   <si>
-    <t>URLEgis_DEV5</t>
+    <t>URLEgis_DEV2</t>
   </si>
 </sst>
 </file>
